--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/1701-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/1701-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6463B107-CF21-4660-B8D7-747A58D3E961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B54FBF0C-3DD8-49A5-8519-45CC3F68123C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{FC2B2FC9-757C-40F3-940D-A4A6BAF1EDE3}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{F1B0CCB0-A1D3-4358-AEC9-70543E50DC9A}"/>
   </bookViews>
   <sheets>
     <sheet name="1701-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1264,21 +1264,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21CE8E8-BBC5-43FE-BB20-732E68D09BF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3174D99-F359-424D-82C8-10FE395E1A2C}">
   <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" customWidth="1"/>
-    <col min="11" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.77734375" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="1" max="3" width="8.6328125" customWidth="1"/>
+    <col min="4" max="6" width="9.08984375" customWidth="1"/>
+    <col min="7" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.6328125" customWidth="1"/>
+    <col min="17" max="17" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1309,7 +1307,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="16"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1360,7 +1358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="17"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1397,7 +1395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
@@ -1450,7 +1448,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2023</v>
       </c>
@@ -1503,7 +1501,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2022</v>
       </c>
@@ -1556,7 +1554,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2021</v>
       </c>
@@ -1609,7 +1607,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2020</v>
       </c>
@@ -1662,7 +1660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2019</v>
       </c>
@@ -1715,7 +1713,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2018</v>
       </c>
@@ -1768,7 +1766,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2017</v>
       </c>
@@ -1821,7 +1819,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2016</v>
       </c>
@@ -1874,7 +1872,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2015</v>
       </c>
@@ -1927,7 +1925,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2014</v>
       </c>
@@ -1980,7 +1978,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2013</v>
       </c>
@@ -2033,7 +2031,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2012</v>
       </c>
@@ -2086,7 +2084,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2011</v>
       </c>
@@ -2139,7 +2137,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2010</v>
       </c>
@@ -2192,7 +2190,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2009</v>
       </c>
@@ -2245,7 +2243,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2008</v>
       </c>
@@ -2298,7 +2296,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="10">
         <v>2007</v>
       </c>
@@ -2351,7 +2349,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2006</v>
       </c>
@@ -2404,7 +2402,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="10">
         <v>2005</v>
       </c>
@@ -2457,7 +2455,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2004</v>
       </c>
@@ -2510,7 +2508,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="10">
         <v>2003</v>
       </c>
@@ -2563,7 +2561,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2002</v>
       </c>
@@ -2616,7 +2614,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="10">
         <v>2001</v>
       </c>
@@ -2669,7 +2667,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>2000</v>
       </c>
@@ -2722,7 +2720,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="10">
         <v>1999</v>
       </c>
@@ -2775,7 +2773,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1998</v>
       </c>
@@ -2828,7 +2826,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="10">
         <v>1997</v>
       </c>
@@ -2881,7 +2879,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A32" s="6">
         <v>1996</v>
       </c>
@@ -2934,7 +2932,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A33" s="10">
         <v>1995</v>
       </c>
@@ -2987,7 +2985,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A34" s="6">
         <v>1994</v>
       </c>
@@ -3040,7 +3038,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A35" s="10">
         <v>1993</v>
       </c>
@@ -3093,7 +3091,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A36" s="6">
         <v>1992</v>
       </c>
@@ -3146,7 +3144,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A37" s="10">
         <v>1991</v>
       </c>
@@ -3199,7 +3197,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A38" s="6">
         <v>1990</v>
       </c>
